--- a/Project-2/Random Synchronization.xlsx
+++ b/Project-2/Random Synchronization.xlsx
@@ -849,6 +849,9 @@
       <c r="A10">
         <v>0.4</v>
       </c>
+      <c r="B10">
+        <v>10</v>
+      </c>
       <c r="C10">
         <v>7</v>
       </c>
